--- a/test_data/gpt.xlsx
+++ b/test_data/gpt.xlsx
@@ -13,10 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="82">
-  <si>
-    <t/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="81">
   <si>
     <t>xxxx xxxx xxxxx xxPCS BOM  (Sample Bill of Materials)</t>
   </si>
@@ -639,31 +636,7 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
       <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" t="s">
-        <v>0</v>
-      </c>
-      <c r="I1" t="s">
         <v>0</v>
       </c>
     </row>
@@ -672,31 +645,31 @@
     <row r="4" spans="1:9" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
         <v>2</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>3</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>4</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>5</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>6</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>7</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>8</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>9</v>
-      </c>
-      <c r="I5" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -704,25 +677,25 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
         <v>12</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>13</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>14</v>
       </c>
-      <c r="G6" t="s">
-        <v>15</v>
-      </c>
       <c r="H6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -730,25 +703,25 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
       <c r="D7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
         <v>18</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>19</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>20</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>21</v>
-      </c>
-      <c r="H7" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -756,25 +729,25 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" t="s">
         <v>24</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>25</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>26</v>
       </c>
-      <c r="G8" t="s">
-        <v>27</v>
-      </c>
       <c r="H8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -782,25 +755,25 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" t="s">
         <v>29</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>30</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>31</v>
       </c>
-      <c r="G9" t="s">
-        <v>32</v>
-      </c>
       <c r="H9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -808,25 +781,25 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" t="s">
         <v>34</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>35</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>36</v>
       </c>
-      <c r="G10" t="s">
-        <v>37</v>
-      </c>
       <c r="H10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -834,25 +807,25 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11">
         <v>2</v>
       </c>
       <c r="D11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" t="s">
         <v>39</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>40</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>41</v>
       </c>
-      <c r="G11" t="s">
-        <v>42</v>
-      </c>
       <c r="H11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -860,25 +833,25 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" t="s">
         <v>44</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>45</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>46</v>
       </c>
-      <c r="G12" t="s">
-        <v>47</v>
-      </c>
       <c r="H12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -886,25 +859,25 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C13">
         <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" t="s">
         <v>49</v>
       </c>
-      <c r="F13" t="s">
-        <v>50</v>
-      </c>
       <c r="G13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -912,25 +885,25 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" t="s">
         <v>52</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>53</v>
       </c>
-      <c r="F14" t="s">
-        <v>54</v>
-      </c>
       <c r="G14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -938,25 +911,25 @@
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" t="s">
         <v>56</v>
       </c>
-      <c r="F15" t="s">
-        <v>57</v>
-      </c>
       <c r="G15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -964,25 +937,25 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C16">
         <v>2</v>
       </c>
       <c r="D16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" t="s">
         <v>59</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>60</v>
       </c>
-      <c r="F16" t="s">
-        <v>61</v>
-      </c>
       <c r="G16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -990,25 +963,25 @@
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" t="s">
         <v>63</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>64</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>65</v>
       </c>
-      <c r="G17" t="s">
-        <v>66</v>
-      </c>
       <c r="H17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -1016,25 +989,25 @@
         <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C18">
         <v>2</v>
       </c>
       <c r="D18" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" t="s">
         <v>68</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>69</v>
       </c>
-      <c r="F18" t="s">
-        <v>70</v>
-      </c>
       <c r="G18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -1042,25 +1015,25 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" t="s">
         <v>72</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>73</v>
       </c>
-      <c r="F19" t="s">
-        <v>74</v>
-      </c>
       <c r="G19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -1068,43 +1041,47 @@
         <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C20">
         <v>2</v>
       </c>
       <c r="D20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E20" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" t="s">
         <v>76</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>77</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>78</v>
-      </c>
-      <c r="H20" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25"/>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25"/>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>3</v>
+      </c>
+    </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -1112,9 +1089,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25"/>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -1122,8 +1101,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25"/>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/test_data/gpt.xlsx
+++ b/test_data/gpt.xlsx
@@ -13,7 +13,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="82">
+  <si>
+    <t/>
+  </si>
   <si>
     <t>xxxx xxxx xxxxx xxPCS BOM  (Sample Bill of Materials)</t>
   </si>
@@ -636,7 +639,31 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
       <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" t="s">
         <v>0</v>
       </c>
     </row>
@@ -645,31 +672,31 @@
     <row r="4" spans="1:9" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -677,25 +704,25 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -703,25 +730,25 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -729,25 +756,25 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -755,25 +782,25 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -781,25 +808,25 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -807,25 +834,25 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C11">
         <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -833,25 +860,25 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -859,25 +886,25 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C13">
         <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -885,25 +912,25 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -911,25 +938,25 @@
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -937,25 +964,25 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C16">
         <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -963,25 +990,25 @@
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -989,25 +1016,25 @@
         <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C18">
         <v>2</v>
       </c>
       <c r="D18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -1015,25 +1042,25 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -1041,47 +1068,43 @@
         <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C20">
         <v>2</v>
       </c>
       <c r="D20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25"/>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>3</v>
-      </c>
-    </row>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25"/>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -1089,11 +1112,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25"/>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -1101,10 +1122,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25"/>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/test_data/gpt.xlsx
+++ b/test_data/gpt.xlsx
@@ -13,13 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="82">
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>xxxx xxxx xxxxx xxPCS BOM  (Sample Bill of Materials)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="80">
   <si>
     <t>Item #</t>
   </si>
@@ -635,7 +629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -643,463 +637,431 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="E1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" t="s">
-        <v>0</v>
-      </c>
-      <c r="I1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25"/>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" t="s">
+        <v>14</v>
+      </c>
+    </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>2</v>
+      <c r="A5">
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" t="s">
-        <v>4</v>
+        <v>26</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="F5" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="G5" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="H5" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="H6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F7" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G7" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="H7" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="F8" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="G8" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="H8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E9" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="F9" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="G9" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="F10" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G10" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G11" t="s">
         <v>40</v>
       </c>
-      <c r="F11" t="s">
-        <v>41</v>
-      </c>
-      <c r="G11" t="s">
-        <v>42</v>
-      </c>
       <c r="H11" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="F12" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="G12" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="E13" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="F13" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="G13" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="H13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="E14" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="F14" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="G14" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="H14" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="E15" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="F15" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="G15" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="H15" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="C16">
         <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E16" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="F16" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="G16" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="H16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>12</v>
-      </c>
-      <c r="B17" t="s">
-        <v>62</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17" t="s">
-        <v>63</v>
-      </c>
-      <c r="E17" t="s">
-        <v>64</v>
-      </c>
-      <c r="F17" t="s">
-        <v>65</v>
-      </c>
-      <c r="G17" t="s">
-        <v>66</v>
-      </c>
-      <c r="H17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>13</v>
-      </c>
-      <c r="B18" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18">
-        <v>2</v>
-      </c>
-      <c r="D18" t="s">
-        <v>68</v>
-      </c>
-      <c r="E18" t="s">
-        <v>69</v>
-      </c>
-      <c r="F18" t="s">
-        <v>70</v>
-      </c>
-      <c r="G18" t="s">
-        <v>16</v>
-      </c>
-      <c r="H18" t="s">
-        <v>16</v>
-      </c>
-    </row>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>14</v>
-      </c>
-      <c r="B19" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19" t="s">
-        <v>72</v>
-      </c>
-      <c r="E19" t="s">
-        <v>73</v>
-      </c>
-      <c r="F19" t="s">
-        <v>74</v>
-      </c>
-      <c r="G19" t="s">
-        <v>16</v>
-      </c>
-      <c r="H19" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20">
-        <v>2</v>
-      </c>
-      <c r="D20" t="s">
-        <v>63</v>
-      </c>
-      <c r="E20" t="s">
-        <v>76</v>
-      </c>
-      <c r="F20" t="s">
-        <v>77</v>
-      </c>
-      <c r="G20" t="s">
+      <c r="A19" t="s">
         <v>78</v>
       </c>
-      <c r="H20" t="s">
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>79</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>81</v>
       </c>
     </row>
   </sheetData>
